--- a/site/Null-Values-Sync-from-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Null-Values-Sync-from-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,95 +551,95 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Source Application Settings</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>h_01KR34W2K98M4PMZ0WMEAN0BT8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KR34W2K98M4PMZ0WMEAN0BT8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Manage Attributes for Null Value Sync and Group Exclusions</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>h_01KR354GGS12T0NHH5BJR5CQG1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KR354GGS12T0NHH5BJR5CQG1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>h_01KR34NFD2VQ1QYT1RDN322AEK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KR34NFD2VQ1QYT1RDN322AEK</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Target System Connection</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,428 +649,98 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>h_01KR35Q4WN9M2S37J6R9YYZ00H</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KR35Q4WN9M2S37J6R9YYZ00H</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manage Cost Centers</t>
+          <t>Match Users Between Source and Target</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>h_01KR35QP2XKQEM14AW9B51FA4F</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KR35QP2XKQEM14AW9B51FA4F</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cost Center Settings</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KQVMYBGQVNVAWK8JY6JC9VHE</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KQVMYBGQVNVAWK8JY6JC9VHE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Provisioning Threshold</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sensitive Fields</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Log Settings</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Report Settings</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Notification Template Settings</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Success Notifications</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Failure Notifications</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Notification Report Settings</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Log Insights</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Debug Mode</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Source Filter</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Null-Values-Sync-from-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
